--- a/artfynd/A 15040-2024 artfynd.xlsx
+++ b/artfynd/A 15040-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>65760554</v>
       </c>
       <c r="B2" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660291.5050831866</v>
+        <v>660292</v>
       </c>
       <c r="R2" t="n">
-        <v>6704294.225447322</v>
+        <v>6704294</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1999-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>65761255</v>
       </c>
       <c r="B3" t="n">
-        <v>95737</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660291.5050831866</v>
+        <v>660292</v>
       </c>
       <c r="R3" t="n">
-        <v>6704294.225447322</v>
+        <v>6704294</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -874,19 +854,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 15040-2024 artfynd.xlsx
+++ b/artfynd/A 15040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65760554</v>
       </c>
       <c r="B2" t="n">
-        <v>98932</v>
+        <v>98933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65761255</v>
       </c>
       <c r="B3" t="n">
-        <v>98130</v>
+        <v>98131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15040-2024 artfynd.xlsx
+++ b/artfynd/A 15040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65760554</v>
       </c>
       <c r="B2" t="n">
-        <v>98933</v>
+        <v>98934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65761255</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>98132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15040-2024 artfynd.xlsx
+++ b/artfynd/A 15040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65760554</v>
       </c>
       <c r="B2" t="n">
-        <v>98934</v>
+        <v>98937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65761255</v>
       </c>
       <c r="B3" t="n">
-        <v>98132</v>
+        <v>98135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15040-2024 artfynd.xlsx
+++ b/artfynd/A 15040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65760554</v>
       </c>
       <c r="B2" t="n">
-        <v>98937</v>
+        <v>98943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65761255</v>
       </c>
       <c r="B3" t="n">
-        <v>98135</v>
+        <v>98141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15040-2024 artfynd.xlsx
+++ b/artfynd/A 15040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65760554</v>
       </c>
       <c r="B2" t="n">
-        <v>98943</v>
+        <v>98946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65761255</v>
       </c>
       <c r="B3" t="n">
-        <v>98141</v>
+        <v>98144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15040-2024 artfynd.xlsx
+++ b/artfynd/A 15040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65760554</v>
       </c>
       <c r="B2" t="n">
-        <v>98946</v>
+        <v>98951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65761255</v>
       </c>
       <c r="B3" t="n">
-        <v>98144</v>
+        <v>98149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15040-2024 artfynd.xlsx
+++ b/artfynd/A 15040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65760554</v>
       </c>
       <c r="B2" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65761255</v>
       </c>
       <c r="B3" t="n">
-        <v>98149</v>
+        <v>98151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15040-2024 artfynd.xlsx
+++ b/artfynd/A 15040-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65760554</v>
+        <v>65761255</v>
       </c>
       <c r="B2" t="n">
-        <v>98953</v>
+        <v>98292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219795</v>
+        <v>569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65761255</v>
+        <v>65760554</v>
       </c>
       <c r="B3" t="n">
-        <v>98151</v>
+        <v>99094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>569</v>
+        <v>219795</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 15040-2024 artfynd.xlsx
+++ b/artfynd/A 15040-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65761255</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65760554</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>